--- a/game46/web.xlsx
+++ b/game46/web.xlsx
@@ -4,14 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="21975" windowHeight="13665"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet5" sheetId="10" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="8" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="9" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="15" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>domain</t>
   </si>
@@ -48,143 +47,100 @@
     <t>json</t>
   </si>
   <si>
-    <t>kludges.fun</t>
-  </si>
-  <si>
-    <t>#bd9683</t>
-  </si>
-  <si>
-    <t>liripipes.fun</t>
-  </si>
-  <si>
-    <t>#38dbf8</t>
-  </si>
-  <si>
-    <t>muntins.fun</t>
-  </si>
-  <si>
-    <t>#ff6b35</t>
-  </si>
-  <si>
-    <t>bricole.cloud</t>
-  </si>
-  <si>
-    <t>#4caf50</t>
-  </si>
-  <si>
-    <t>camess.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sec.logorrhea.site
-</t>
-  </si>
-  <si>
-    <t>sec.horizonfun.fun</t>
-  </si>
-  <si>
-    <t>#c9a87a</t>
-  </si>
-  <si>
-    <t>sedulitys.top</t>
-  </si>
-  <si>
-    <t>#f7ece7</t>
-  </si>
-  <si>
-    <t>#a61b29</t>
-  </si>
-  <si>
-    <t>conatuss.top</t>
-  </si>
-  <si>
-    <t>#e2e1dd</t>
-  </si>
-  <si>
-    <t>#8abe98</t>
-  </si>
-  <si>
-    <t>droshky.fun</t>
-  </si>
-  <si>
-    <t>#fafbe6</t>
-  </si>
-  <si>
-    <t>#a48ce6</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#c6e6e8</t>
-  </si>
-  <si>
-    <t>#373834</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#e3e3e5</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>invicts.site</t>
-  </si>
-  <si>
-    <t>#e7bf40</t>
-  </si>
-  <si>
-    <t>halcyons.cloud</t>
-  </si>
-  <si>
-    <t>#a4dd52</t>
-  </si>
-  <si>
-    <t>plodfuns.fun</t>
-  </si>
-  <si>
-    <t>threaps.fun</t>
-  </si>
-  <si>
-    <t>#bdeae5</t>
-  </si>
-  <si>
-    <t>dfgtime.top</t>
-  </si>
-  <si>
-    <t>#36B06F</t>
-  </si>
-  <si>
-    <t>#a37070</t>
-  </si>
-  <si>
-    <t>assiduitys.site</t>
-  </si>
-  <si>
-    <t>#ff9988</t>
-  </si>
-  <si>
-    <t>#4167b1</t>
-  </si>
-  <si>
-    <t>conatives.site</t>
-  </si>
-  <si>
-    <t>#30abc5</t>
-  </si>
-  <si>
-    <t>#d62828</t>
-  </si>
-  <si>
-    <t>#e58889</t>
-  </si>
-  <si>
-    <t>#b57743</t>
-  </si>
-  <si>
-    <t>#f5f4f7</t>
+    <t>play.eximious.site</t>
+  </si>
+  <si>
+    <t>#27456c</t>
+  </si>
+  <si>
+    <t>sec.eximious.site</t>
+  </si>
+  <si>
+    <t>#98b0ca</t>
+  </si>
+  <si>
+    <t>play.feateous.site</t>
+  </si>
+  <si>
+    <t>#e3a841</t>
+  </si>
+  <si>
+    <t>sec.feateous.site</t>
+  </si>
+  <si>
+    <t>#bdd0c4</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>spiraling.cloud</t>
+  </si>
+  <si>
+    <t>#664b3a</t>
+  </si>
+  <si>
+    <t>silvanium.cloud</t>
+  </si>
+  <si>
+    <t>#e07563</t>
+  </si>
+  <si>
+    <t>seabluee.com</t>
+  </si>
+  <si>
+    <t>#f8d09d</t>
+  </si>
+  <si>
+    <t>haberdasher.cloud</t>
+  </si>
+  <si>
+    <t>#fb9966</t>
+  </si>
+  <si>
+    <t>melancholy.cloud</t>
+  </si>
+  <si>
+    <t>#afcd53</t>
+  </si>
+  <si>
+    <t>insulary.fun</t>
+  </si>
+  <si>
+    <t>#ed6d46</t>
+  </si>
+  <si>
+    <t>vapourous.fun</t>
+  </si>
+  <si>
+    <t>#7d929f</t>
+  </si>
+  <si>
+    <t>unsdgaction.com</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
+    <t>周一</t>
+  </si>
+  <si>
+    <t>周二</t>
+  </si>
+  <si>
+    <t>周三</t>
+  </si>
+  <si>
+    <t>周四</t>
+  </si>
+  <si>
+    <t>周五</t>
+  </si>
+  <si>
+    <t>周六</t>
+  </si>
+  <si>
+    <t>周日</t>
   </si>
 </sst>
 </file>
@@ -197,7 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -206,9 +162,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -221,51 +177,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="9"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFCE9178"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -277,6 +193,44 @@
     </font>
     <font>
       <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
@@ -412,7 +366,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="60">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,163 +375,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBD9683"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDEAE5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF36B06F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7ECE7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA37070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9988"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E1DD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4167B1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30ABC5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD62828"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E6E8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE58889"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3E3E5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB57743"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F4F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA61B29"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7BF40"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4DD52"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ABE98"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA48CE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF373834"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF707899"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEA23"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38DBF8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF6B35"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CAF50"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFB9966"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFCD53"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED6D46"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7D929F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDBB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF664B3A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE07563"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D09D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27456C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98B0CA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3A841"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD0C4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -877,85 +747,127 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -964,10 +876,10 @@
     <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -976,155 +888,75 @@
     <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1179,6 +1011,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <mruColors>
+      <color rgb="00F4F207"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1509,13 +1346,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1532,84 +1369,95 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="3">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="32" t="s">
+      <c r="E5" s="3">
         <v>8</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="kludges.fun"/>
-    <hyperlink ref="A3" r:id="rId2" display="liripipes.fun"/>
-    <hyperlink ref="A4" r:id="rId3" display="muntins.fun"/>
-    <hyperlink ref="A5" r:id="rId4" display="bricole.cloud"/>
-    <hyperlink ref="A6" r:id="rId5" display="camess.site"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1618,67 +1466,211 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="22.5" spans="1:5">
-      <c r="A2" s="27" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="29"/>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="30" t="s">
+      <c r="B2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="C2" s="12"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
+      <c r="B3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="12"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="15"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="15"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="sec.logorrhea.site&#10;"/>
+    <hyperlink ref="F16" r:id="rId1"/>
+    <hyperlink ref="F17" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1688,13 +1680,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="28.875" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1704,69 +1696,86 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>31</v>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="sedulitys.top"/>
-    <hyperlink ref="A3" r:id="rId2" display="conatuss.top"/>
-    <hyperlink ref="A4" r:id="rId3" display="droshky.fun"/>
-    <hyperlink ref="A5" r:id="rId4" display="spuddles.fun"/>
-    <hyperlink ref="A6" r:id="rId5" display="moilfuns.fun"/>
+    <hyperlink ref="A6" r:id="rId1" display="unsdgaction.com" tooltip="https://unsdgaction.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1776,188 +1785,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="F1" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="D2" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="invicts.site"/>
-    <hyperlink ref="A3" r:id="rId2" display="halcyons.cloud"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="17.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="I6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:10">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="I7" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="I8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="I9" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1"/>
-    <hyperlink ref="A8" r:id="rId2"/>
-    <hyperlink ref="A11" r:id="rId3"/>
-    <hyperlink ref="A2" r:id="rId4" display="plodfuns.fun"/>
-    <hyperlink ref="A3" r:id="rId5" display="threaps.fun"/>
-    <hyperlink ref="A5" r:id="rId6" display="assiduitys.site"/>
-    <hyperlink ref="A6" r:id="rId7" display="conatives.site"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/game46/web.xlsx
+++ b/game46/web.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21975" windowHeight="13665"/>
+    <workbookView windowWidth="19815" windowHeight="10890"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="15" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="14" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="15" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>domain</t>
   </si>
@@ -47,79 +47,73 @@
     <t>json</t>
   </si>
   <si>
-    <t>play.eximious.site</t>
-  </si>
-  <si>
-    <t>#27456c</t>
-  </si>
-  <si>
-    <t>sec.eximious.site</t>
-  </si>
-  <si>
-    <t>#98b0ca</t>
-  </si>
-  <si>
-    <t>play.feateous.site</t>
-  </si>
-  <si>
-    <t>#e3a841</t>
-  </si>
-  <si>
-    <t>sec.feateous.site</t>
-  </si>
-  <si>
-    <t>#bdd0c4</t>
+    <t>effulgent.cloud</t>
+  </si>
+  <si>
+    <t>#ed6d46</t>
+  </si>
+  <si>
+    <t>jazerant.cloud</t>
+  </si>
+  <si>
+    <t>#7d929f</t>
+  </si>
+  <si>
+    <t>divinator.cloud</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
+    <t>feuilleton.cloud</t>
+  </si>
+  <si>
+    <t>#b65458</t>
   </si>
   <si>
     <t>color</t>
   </si>
   <si>
-    <t>spiraling.cloud</t>
-  </si>
-  <si>
-    <t>#664b3a</t>
-  </si>
-  <si>
-    <t>silvanium.cloud</t>
-  </si>
-  <si>
-    <t>#e07563</t>
-  </si>
-  <si>
-    <t>seabluee.com</t>
-  </si>
-  <si>
-    <t>#f8d09d</t>
-  </si>
-  <si>
-    <t>haberdasher.cloud</t>
-  </si>
-  <si>
-    <t>#fb9966</t>
-  </si>
-  <si>
-    <t>melancholy.cloud</t>
-  </si>
-  <si>
-    <t>#afcd53</t>
-  </si>
-  <si>
-    <t>insulary.fun</t>
-  </si>
-  <si>
-    <t>#ed6d46</t>
-  </si>
-  <si>
-    <t>vapourous.fun</t>
-  </si>
-  <si>
-    <t>#7d929f</t>
-  </si>
-  <si>
-    <t>unsdgaction.com</t>
-  </si>
-  <si>
-    <t>#ddbb99</t>
+    <t>date</t>
+  </si>
+  <si>
+    <t>read.xenolith.fun</t>
+  </si>
+  <si>
+    <t>#fac03d</t>
+  </si>
+  <si>
+    <t>sec.xenolith.fun</t>
+  </si>
+  <si>
+    <t>#5c4f55</t>
+  </si>
+  <si>
+    <t>play.kaleidos.fun</t>
+  </si>
+  <si>
+    <t>#f53d93</t>
+  </si>
+  <si>
+    <t>sec.kaleidos.fun</t>
+  </si>
+  <si>
+    <t>#ff978a</t>
+  </si>
+  <si>
+    <t>play.fervid.site</t>
+  </si>
+  <si>
+    <t>#6ae966</t>
+  </si>
+  <si>
+    <t>sec.fervid.site</t>
+  </si>
+  <si>
+    <t>#a515f9</t>
+  </si>
+  <si>
+    <t>日期</t>
   </si>
   <si>
     <t>周一</t>
@@ -147,13 +141,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -170,6 +165,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -178,7 +188,49 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <color rgb="FFFBF1D7"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -193,44 +245,6 @@
     </font>
     <font>
       <u/>
-      <sz val="10"/>
-      <color rgb="FF2972F4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
@@ -366,7 +380,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="47">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,13 +395,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFB9966"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFCD53"/>
+        <fgColor rgb="FFF53D93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE63946"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF978A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AE966"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA515F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAC03D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9874"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5C4F55"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,6 +449,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDEF0F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF7D929F"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -411,43 +467,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF664B3A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE07563"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D09D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27456C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98B0CA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3A841"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD0C4"/>
+        <fgColor rgb="FFB65458"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -747,31 +767,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -780,132 +788,148 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -913,49 +937,52 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1346,13 +1373,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="26.375" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1369,95 +1396,122 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3">
+      <c r="C2" s="22"/>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="7">
         <v>2</v>
       </c>
-      <c r="E2" s="3">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
+      <c r="E3" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="7">
         <v>3</v>
       </c>
-      <c r="E3" s="3">
-        <v>8</v>
-      </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="3">
+      <c r="E4" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="7">
         <v>4</v>
       </c>
-      <c r="E4" s="3">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="3">
+      <c r="E5" s="7">
         <v>5</v>
       </c>
-      <c r="E5" s="3">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A8" r:id="rId1"/>
+    <hyperlink ref="A9" r:id="rId2"/>
+    <hyperlink ref="A10" r:id="rId3"/>
+    <hyperlink ref="A11" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1466,10 +1520,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="27.75" customWidth="1"/>
+    <col min="4" max="4" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1482,190 +1537,198 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="B2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14">
+        <v>46144</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="12"/>
+      <c r="B3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14">
+        <v>46176</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="15"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="15"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="D21" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1680,13 +1743,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="1" max="1" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1703,80 +1766,95 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7">
+        <v>16</v>
+      </c>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7">
+        <v>16</v>
+      </c>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="7">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="4"/>
+      <c r="D5" s="7">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
+      <c r="E5" s="7">
+        <v>16</v>
+      </c>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="7"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" display="unsdgaction.com" tooltip="https://unsdgaction.com"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1785,34 +1863,37 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="D2" s="2"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="E2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/game46/web.xlsx
+++ b/game46/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="10890"/>
+    <workbookView windowWidth="14475" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="15" r:id="rId1"/>
@@ -47,28 +47,16 @@
     <t>json</t>
   </si>
   <si>
-    <t>effulgent.cloud</t>
-  </si>
-  <si>
-    <t>#ed6d46</t>
-  </si>
-  <si>
-    <t>jazerant.cloud</t>
-  </si>
-  <si>
-    <t>#7d929f</t>
-  </si>
-  <si>
-    <t>divinator.cloud</t>
-  </si>
-  <si>
-    <t>#ddbb99</t>
-  </si>
-  <si>
-    <t>feuilleton.cloud</t>
-  </si>
-  <si>
-    <t>#b65458</t>
+    <t>play.grapho.fun</t>
+  </si>
+  <si>
+    <t>#145f39</t>
+  </si>
+  <si>
+    <t>sec.grapho.fun</t>
+  </si>
+  <si>
+    <t>#4189b3</t>
   </si>
   <si>
     <t>color</t>
@@ -77,16 +65,28 @@
     <t>date</t>
   </si>
   <si>
-    <t>read.xenolith.fun</t>
-  </si>
-  <si>
-    <t>#fac03d</t>
-  </si>
-  <si>
-    <t>sec.xenolith.fun</t>
-  </si>
-  <si>
-    <t>#5c4f55</t>
+    <t>read.walrussea.com</t>
+  </si>
+  <si>
+    <t>#0c567d</t>
+  </si>
+  <si>
+    <t>sec.walrussea.com</t>
+  </si>
+  <si>
+    <t>#01847f</t>
+  </si>
+  <si>
+    <t>read.seacalmy.com</t>
+  </si>
+  <si>
+    <t>#ed9874</t>
+  </si>
+  <si>
+    <t>sec.seacalmy.com</t>
+  </si>
+  <si>
+    <t>#425066</t>
   </si>
   <si>
     <t>play.kaleidos.fun</t>
@@ -148,7 +148,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -189,6 +189,14 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FFFBF1D7"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -222,8 +230,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -380,7 +389,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="47">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,7 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAC03D"/>
+        <fgColor rgb="FF0C567D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF01847F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -437,37 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5C4F55"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED6D46"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF0F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7D929F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDBB99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB65458"/>
+        <fgColor rgb="FF425066"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF145F39"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4189B3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -767,79 +764,85 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -848,10 +851,10 @@
     <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -860,10 +863,10 @@
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -872,10 +875,10 @@
     <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -884,10 +887,10 @@
     <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -896,23 +899,17 @@
     <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -940,49 +937,46 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1397,92 +1391,76 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="7">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23">
         <v>1</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="7">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23">
         <v>2</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="7">
-        <v>3</v>
-      </c>
-      <c r="E4" s="7">
-        <v>5</v>
-      </c>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="7">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7">
-        <v>5</v>
-      </c>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="20"/>
@@ -1511,6 +1489,8 @@
     <hyperlink ref="A9" r:id="rId2"/>
     <hyperlink ref="A10" r:id="rId3"/>
     <hyperlink ref="A11" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5" tooltip="http://gravecaller.com"/>
+    <hyperlink ref="A7" r:id="rId5" tooltip="http://gravecaller.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1532,50 +1512,54 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="14">
-        <v>46144</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="13"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="14">
-        <v>46176</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="17"/>
@@ -1734,6 +1718,10 @@
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1"/>
     <hyperlink ref="F17" r:id="rId2"/>
+    <hyperlink ref="A2" r:id="rId3" display="read.walrussea.com" tooltip="http://read.walrussea.com"/>
+    <hyperlink ref="A3" r:id="rId4" display="sec.walrussea.com" tooltip="http://sec.walrussea.com"/>
+    <hyperlink ref="A4" r:id="rId5" display="read.seacalmy.com" tooltip="http://seacalmy.com"/>
+    <hyperlink ref="A5" r:id="rId5" display="sec.seacalmy.com" tooltip="http://seacalmy.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
